--- a/data/trans_orig/DC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023</t>
+          <t>Población con dolor crónico (incluye Otro dolor crónico) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>170546</t>
+          <t>172840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212187</t>
+          <t>212679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>423347</t>
+          <t>422083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>465882</t>
+          <t>464422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>606150</t>
+          <t>605636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>664414</t>
+          <t>665008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,34%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302751</t>
+          <t>302259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344392</t>
+          <t>342098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>289626</t>
+          <t>291086</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>332161</t>
+          <t>333425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>606032</t>
+          <t>605438</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>664296</t>
+          <t>664810</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>317942</t>
+          <t>302841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>511254</t>
+          <t>508312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>792327</t>
+          <t>807628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1284690</t>
+          <t>1337089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1180441</t>
+          <t>1158747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1911631</t>
+          <t>1844559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1779073</t>
+          <t>1782015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1972385</t>
+          <t>1987486</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>953133</t>
+          <t>900734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1445496</t>
+          <t>1430195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2616519</t>
+          <t>2683591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3347709</t>
+          <t>3369403</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90998</t>
+          <t>92096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>128446</t>
+          <t>129922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201344</t>
+          <t>199657</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243419</t>
+          <t>243073</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303040</t>
+          <t>302294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363431</t>
+          <t>362333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518177</t>
+          <t>516701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>555625</t>
+          <t>554527</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417044</t>
+          <t>417390</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>459119</t>
+          <t>460806</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>943655</t>
+          <t>944753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004046</t>
+          <t>1004792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>577361</t>
+          <t>582504</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>821662</t>
+          <t>813866</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1473531</t>
+          <t>1476708</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2011005</t>
+          <t>1988583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2118321</t>
+          <t>2118359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2830440</t>
+          <t>2797662</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,37%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2630227</t>
+          <t>2638023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2874528</t>
+          <t>2869385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1642789</t>
+          <t>1665211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2180263</t>
+          <t>2177086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4275243</t>
+          <t>4308021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4987362</t>
+          <t>4987324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/DC_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/DC_R-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>192378</t>
+          <t>206748</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172840</t>
+          <t>185330</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212679</t>
+          <t>228230</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>444551</t>
+          <t>483088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>422083</t>
+          <t>460512</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>464422</t>
+          <t>504583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>636929</t>
+          <t>689835</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>605636</t>
+          <t>655921</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>665008</t>
+          <t>722264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>322560</t>
+          <t>371781</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>302259</t>
+          <t>350299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>342098</t>
+          <t>393199</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>310957</t>
+          <t>338950</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>291086</t>
+          <t>317455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>333425</t>
+          <t>361526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>633517</t>
+          <t>710732</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>605438</t>
+          <t>678303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>664810</t>
+          <t>744646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>441162</t>
+          <t>477496</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>302841</t>
+          <t>435723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>508312</t>
+          <t>519571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>963255</t>
+          <t>779539</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>807628</t>
+          <t>741949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1337089</t>
+          <t>823707</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1404417</t>
+          <t>1257036</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1158747</t>
+          <t>1195314</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1844559</t>
+          <t>1319782</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1849165</t>
+          <t>1753070</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1782015</t>
+          <t>1710995</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1987486</t>
+          <t>1794843</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1274568</t>
+          <t>1391853</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900734</t>
+          <t>1347685</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1430195</t>
+          <t>1429443</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3123733</t>
+          <t>3144923</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2683591</t>
+          <t>3082177</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3369403</t>
+          <t>3206645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>72,85%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>110053</t>
+          <t>120718</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92096</t>
+          <t>100466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129922</t>
+          <t>141017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>222877</t>
+          <t>249443</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>199657</t>
+          <t>226537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243073</t>
+          <t>273835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>332930</t>
+          <t>370161</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>302294</t>
+          <t>338258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>362333</t>
+          <t>403089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>536570</t>
+          <t>590869</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516701</t>
+          <t>570570</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>554527</t>
+          <t>611121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>437586</t>
+          <t>485434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417390</t>
+          <t>461042</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>460806</t>
+          <t>508340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>974156</t>
+          <t>1076303</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>944753</t>
+          <t>1043375</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1004792</t>
+          <t>1108206</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>743594</t>
+          <t>804962</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>582504</t>
+          <t>751680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>813866</t>
+          <t>856982</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1630683</t>
+          <t>1512070</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1476708</t>
+          <t>1460343</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1988583</t>
+          <t>1565583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2374277</t>
+          <t>2317032</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2118359</t>
+          <t>2247390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2797662</t>
+          <t>2397803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2708295</t>
+          <t>2715721</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2638023</t>
+          <t>2663701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2869385</t>
+          <t>2769003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2023111</t>
+          <t>2216237</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1665211</t>
+          <t>2162724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2177086</t>
+          <t>2267964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4731406</t>
+          <t>4931958</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4308021</t>
+          <t>4851187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4987324</t>
+          <t>5001600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
